--- a/artfynd/A 10014-2025 artfynd.xlsx
+++ b/artfynd/A 10014-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123332350</v>
+        <v>123332348</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>184</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441962</v>
+        <v>441977</v>
       </c>
       <c r="R2" t="n">
-        <v>6461395</v>
+        <v>6461401</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123332351</v>
+        <v>123332350</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441968</v>
+        <v>441962</v>
       </c>
       <c r="R3" t="n">
-        <v>6461417</v>
+        <v>6461395</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123332349</v>
+        <v>123332351</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441932</v>
+        <v>441968</v>
       </c>
       <c r="R4" t="n">
-        <v>6461406</v>
+        <v>6461417</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123332348</v>
+        <v>123332349</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>132</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441977</v>
+        <v>441932</v>
       </c>
       <c r="R5" t="n">
-        <v>6461401</v>
+        <v>6461406</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 10014-2025 artfynd.xlsx
+++ b/artfynd/A 10014-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123332348</v>
+        <v>123332351</v>
       </c>
       <c r="B2" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441977</v>
+        <v>441968</v>
       </c>
       <c r="R2" t="n">
-        <v>6461401</v>
+        <v>6461417</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123332350</v>
+        <v>123332348</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>184</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441962</v>
+        <v>441977</v>
       </c>
       <c r="R3" t="n">
-        <v>6461395</v>
+        <v>6461401</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123332351</v>
+        <v>123332350</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441968</v>
+        <v>441962</v>
       </c>
       <c r="R4" t="n">
-        <v>6461417</v>
+        <v>6461395</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1032,7 +1032,7 @@
         <v>123332349</v>
       </c>
       <c r="B5" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 10014-2025 artfynd.xlsx
+++ b/artfynd/A 10014-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123332351</v>
+        <v>123332350</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441968</v>
+        <v>441962</v>
       </c>
       <c r="R2" t="n">
-        <v>6461417</v>
+        <v>6461395</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123332348</v>
+        <v>123332351</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441977</v>
+        <v>441968</v>
       </c>
       <c r="R3" t="n">
-        <v>6461401</v>
+        <v>6461417</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123332350</v>
+        <v>123332349</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>132</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441962</v>
+        <v>441932</v>
       </c>
       <c r="R4" t="n">
-        <v>6461395</v>
+        <v>6461406</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123332349</v>
+        <v>123332348</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>184</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441932</v>
+        <v>441977</v>
       </c>
       <c r="R5" t="n">
-        <v>6461406</v>
+        <v>6461401</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 10014-2025 artfynd.xlsx
+++ b/artfynd/A 10014-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123332350</v>
+        <v>123332348</v>
       </c>
       <c r="B2" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>184</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441962</v>
+        <v>441977</v>
       </c>
       <c r="R2" t="n">
-        <v>6461395</v>
+        <v>6461401</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -796,7 +796,7 @@
         <v>123332351</v>
       </c>
       <c r="B3" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123332349</v>
+        <v>123332350</v>
       </c>
       <c r="B4" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441932</v>
+        <v>441962</v>
       </c>
       <c r="R4" t="n">
-        <v>6461406</v>
+        <v>6461395</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123332348</v>
+        <v>123332349</v>
       </c>
       <c r="B5" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>132</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441977</v>
+        <v>441932</v>
       </c>
       <c r="R5" t="n">
-        <v>6461401</v>
+        <v>6461406</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 10014-2025 artfynd.xlsx
+++ b/artfynd/A 10014-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123332348</v>
       </c>
       <c r="B2" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>123332351</v>
       </c>
       <c r="B3" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>123332350</v>
       </c>
       <c r="B4" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>123332349</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 10014-2025 artfynd.xlsx
+++ b/artfynd/A 10014-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123332348</v>
+        <v>123332349</v>
       </c>
       <c r="B2" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>132</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441977</v>
+        <v>441932</v>
       </c>
       <c r="R2" t="n">
-        <v>6461401</v>
+        <v>6461406</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123332351</v>
+        <v>123332350</v>
       </c>
       <c r="B3" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441968</v>
+        <v>441962</v>
       </c>
       <c r="R3" t="n">
-        <v>6461417</v>
+        <v>6461395</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123332350</v>
+        <v>123332351</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441962</v>
+        <v>441968</v>
       </c>
       <c r="R4" t="n">
-        <v>6461395</v>
+        <v>6461417</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123332349</v>
+        <v>123332348</v>
       </c>
       <c r="B5" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>184</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441932</v>
+        <v>441977</v>
       </c>
       <c r="R5" t="n">
-        <v>6461406</v>
+        <v>6461401</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 10014-2025 artfynd.xlsx
+++ b/artfynd/A 10014-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123332349</v>
+        <v>123332350</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441932</v>
+        <v>441962</v>
       </c>
       <c r="R2" t="n">
-        <v>6461406</v>
+        <v>6461395</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123332350</v>
+        <v>123332349</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>132</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441962</v>
+        <v>441932</v>
       </c>
       <c r="R3" t="n">
-        <v>6461395</v>
+        <v>6461406</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123332351</v>
+        <v>123332348</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>184</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441968</v>
+        <v>441977</v>
       </c>
       <c r="R4" t="n">
-        <v>6461417</v>
+        <v>6461401</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123332348</v>
+        <v>123332351</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441977</v>
+        <v>441968</v>
       </c>
       <c r="R5" t="n">
-        <v>6461401</v>
+        <v>6461417</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 10014-2025 artfynd.xlsx
+++ b/artfynd/A 10014-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123332350</v>
+        <v>123332348</v>
       </c>
       <c r="B2" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>184</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441962</v>
+        <v>441977</v>
       </c>
       <c r="R2" t="n">
-        <v>6461395</v>
+        <v>6461401</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123332349</v>
+        <v>123332350</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441932</v>
+        <v>441962</v>
       </c>
       <c r="R3" t="n">
-        <v>6461406</v>
+        <v>6461395</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123332348</v>
+        <v>123332351</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441977</v>
+        <v>441968</v>
       </c>
       <c r="R4" t="n">
-        <v>6461401</v>
+        <v>6461417</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123332351</v>
+        <v>123332349</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>132</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441968</v>
+        <v>441932</v>
       </c>
       <c r="R5" t="n">
-        <v>6461417</v>
+        <v>6461406</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 10014-2025 artfynd.xlsx
+++ b/artfynd/A 10014-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123332350</v>
+        <v>123332349</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -828,7 +828,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>132</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441962</v>
+        <v>441932</v>
       </c>
       <c r="R3" t="n">
-        <v>6461395</v>
+        <v>6461406</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -1029,7 +1029,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123332349</v>
+        <v>123332350</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441932</v>
+        <v>441962</v>
       </c>
       <c r="R5" t="n">
-        <v>6461406</v>
+        <v>6461395</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 10014-2025 artfynd.xlsx
+++ b/artfynd/A 10014-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123332348</v>
+        <v>123332349</v>
       </c>
       <c r="B2" t="n">
         <v>98079</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>132</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441977</v>
+        <v>441932</v>
       </c>
       <c r="R2" t="n">
-        <v>6461401</v>
+        <v>6461406</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -793,7 +793,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123332349</v>
+        <v>123332350</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -828,7 +828,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441932</v>
+        <v>441962</v>
       </c>
       <c r="R3" t="n">
-        <v>6461406</v>
+        <v>6461395</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -1029,7 +1029,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123332350</v>
+        <v>123332348</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>184</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441962</v>
+        <v>441977</v>
       </c>
       <c r="R5" t="n">
-        <v>6461395</v>
+        <v>6461401</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 10014-2025 artfynd.xlsx
+++ b/artfynd/A 10014-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123332349</v>
+        <v>123332350</v>
       </c>
       <c r="B2" t="n">
         <v>98079</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441932</v>
+        <v>441962</v>
       </c>
       <c r="R2" t="n">
-        <v>6461406</v>
+        <v>6461395</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -793,7 +793,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123332350</v>
+        <v>123332349</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -828,7 +828,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>132</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441962</v>
+        <v>441932</v>
       </c>
       <c r="R3" t="n">
-        <v>6461395</v>
+        <v>6461406</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>

--- a/artfynd/A 10014-2025 artfynd.xlsx
+++ b/artfynd/A 10014-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123332350</v>
+        <v>123332351</v>
       </c>
       <c r="B2" t="n">
         <v>98079</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441962</v>
+        <v>441968</v>
       </c>
       <c r="R2" t="n">
-        <v>6461395</v>
+        <v>6461417</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -793,7 +793,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123332349</v>
+        <v>123332348</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -828,7 +828,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>184</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441932</v>
+        <v>441977</v>
       </c>
       <c r="R3" t="n">
-        <v>6461406</v>
+        <v>6461401</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123332351</v>
+        <v>123332350</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -946,7 +946,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441968</v>
+        <v>441962</v>
       </c>
       <c r="R4" t="n">
-        <v>6461417</v>
+        <v>6461395</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1029,7 +1029,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123332348</v>
+        <v>123332349</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>132</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441977</v>
+        <v>441932</v>
       </c>
       <c r="R5" t="n">
-        <v>6461401</v>
+        <v>6461406</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 10014-2025 artfynd.xlsx
+++ b/artfynd/A 10014-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123332351</v>
+        <v>123332348</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>184</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441968</v>
+        <v>441977</v>
       </c>
       <c r="R2" t="n">
-        <v>6461417</v>
+        <v>6461401</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -793,15 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123332348</v>
+        <v>123332349</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -828,7 +818,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>132</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -845,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441977</v>
+        <v>441932</v>
       </c>
       <c r="R3" t="n">
-        <v>6461401</v>
+        <v>6461406</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -914,12 +904,7 @@
         <v>123332350</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,15 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123332349</v>
+        <v>123332351</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1064,7 +1044,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1081,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441932</v>
+        <v>441968</v>
       </c>
       <c r="R5" t="n">
-        <v>6461406</v>
+        <v>6461417</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 10014-2025 artfynd.xlsx
+++ b/artfynd/A 10014-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123332348</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123332349</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123332350</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,8 +1144,19 @@
           <t>Skogsgruppen Skaraborg</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123332351</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>